--- a/exports/asset_report.xlsx
+++ b/exports/asset_report.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,6 +415,15 @@
   </sheetPr>
   <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -666,7 +675,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Assigned</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
